--- a/data/middlesex-senate-primary-2026-results.xlsx
+++ b/data/middlesex-senate-primary-2026-results.xlsx
@@ -73,10 +73,6 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00A03020"/>
-    </font>
-    <font>
       <i val="1"/>
       <sz val="10"/>
     </font>
@@ -86,6 +82,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00A03020"/>
     </font>
   </fonts>
   <fills count="7">
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -175,13 +175,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1250,14 +1247,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1278,12 +1274,7 @@
       </c>
       <c r="D1" s="14" t="inlineStr">
         <is>
-          <t>Precinct count</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Verified?</t>
+          <t>Reporting unit</t>
         </is>
       </c>
     </row>
@@ -1303,10 +1294,9 @@
           <t>Somerville</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr"/>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1326,10 +1316,9 @@
           <t>Medford</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr"/>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1349,10 +1338,9 @@
           <t>Cambridge W9-11</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr"/>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1360,9 @@
           <t>Winchester P4, Winchester P5, Winchester P6, Winchester P7</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>4 precincts, entered separately</t>
         </is>
       </c>
     </row>
@@ -1397,10 +1382,9 @@
           <t>Malden</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1420,10 +1404,9 @@
           <t>Melrose</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1443,10 +1426,9 @@
           <t>Reading</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1466,10 +1448,9 @@
           <t>Stoneham</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1489,10 +1470,9 @@
           <t>Wakefield</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>TO VERIFY</t>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>one town-level total</t>
         </is>
       </c>
     </row>
@@ -1512,41 +1492,38 @@
           <t>Winchester P1, Winchester P2, Winchester P3, Winchester P8</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>4 precincts, entered separately</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Fill in the precinct counts from the Secretary of the Commonwealth or each clerk, then copy them into RACES[].communities[].precincts in index.html. Until every community in a district has a number, the page counts communities only and hides the precinct line.</t>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>The reporting unit is the community. Only Winchester is broken out precinct by precinct, because that is where our reporters are; every other city and town is entered as one posted total. The page counts communities and does not print a district-wide precinct denominator.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Candidates as configured</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Race</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
@@ -1689,7 +1666,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>VERIFY every name, spelling and ballot order against the official ballot before polls close.</t>
         </is>

--- a/data/middlesex-senate-primary-2026-results.xlsx
+++ b/data/middlesex-senate-primary-2026-results.xlsx
@@ -1247,13 +1247,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1277,6 +1278,11 @@
           <t>Reporting unit</t>
         </is>
       </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Precincts</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -1299,6 +1305,9 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E2" s="15" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -1321,6 +1330,9 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E3" s="15" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -1343,6 +1355,11 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>TO ESTABLISH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -1365,6 +1382,9 @@
           <t>4 precincts, entered separately</t>
         </is>
       </c>
+      <c r="E5" s="15" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -1387,6 +1407,9 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E6" s="15" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -1409,6 +1432,9 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E7" s="15" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -1431,6 +1457,9 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E8" s="15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -1453,6 +1482,9 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E9" s="15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -1475,6 +1507,9 @@
           <t>one town-level total</t>
         </is>
       </c>
+      <c r="E10" s="15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -1497,11 +1532,14 @@
           <t>4 precincts, entered separately</t>
         </is>
       </c>
+      <c r="E11" s="15" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>The reporting unit is the community. Only Winchester is broken out precinct by precinct, because that is where our reporters are; every other city and town is entered as one posted total. The page counts communities and does not print a district-wide precinct denominator.</t>
+          <t>Entry is by community: only Winchester is typed precinct by precinct. The Precincts column is the denominator for the page's secondary "N of M precincts" line - when a city posts its citywide total, all of its precincts count at once. The 5th Middlesex totals 67. The 2nd Middlesex shows no precinct line until Cambridge's ward composition is settled.</t>
         </is>
       </c>
     </row>

--- a/data/middlesex-senate-primary-2026-results.xlsx
+++ b/data/middlesex-senate-primary-2026-results.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Cambridge W9-11</t>
+          <t>Cambridge W10 W11 W7-1 W8-1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -668,7 +668,7 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>White cells only: Somerville, Medford, Cambridge (wards 9-11), Winchester (precincts 4-7)</t>
+          <t>White cells only: Somerville, Medford, Cambridge (Wards 10, 11 + 7-1, 8-1), Winchester (precincts 4-7)</t>
         </is>
       </c>
       <c r="D2" s="3" t="n"/>
@@ -1177,14 +1177,14 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Every other community - that city or town's own posted results, entered as one total per candidate. Somerville, Medford and Cambridge wards 9-11 for the 2nd Middlesex; Malden, Melrose, Reading, Stoneham and Wakefield for the 5th.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+          <t>Every other community - that city or town's own posted results, entered as one total per candidate. Somerville, Medford and the Cambridge portion for the 2nd Middlesex; Malden, Melrose, Reading, Stoneham and Wakefield for the 5th.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Cambridge is in the 2nd Middlesex only for WARDS 9, 10 and 11. Do not enter a citywide Cambridge total - it would count voters who are not in this district.</t>
+          <t>Cambridge is in the 2nd Middlesex only for WARDS 10 and 11 plus Ward 7 Precinct 1 and Ward 8 Precinct 1 - eleven reporting units in all. Ward 9 is NOT in this district. Do not enter a citywide Cambridge total: it would count voters who are not in this district.</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Cambridge (wards 9-11)</t>
+          <t>Cambridge (Wards 10, 11 + 7-1, 8-1)</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Cambridge W9-11</t>
+          <t>Cambridge W10 W11 W7-1 W8-1</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
@@ -1355,10 +1355,8 @@
           <t>one town-level total</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>TO ESTABLISH</t>
-        </is>
+      <c r="E4" s="15" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="5">

--- a/data/middlesex-senate-primary-2026-results.xlsx
+++ b/data/middlesex-senate-primary-2026-results.xlsx
@@ -65,7 +65,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001D4E6B"/>
+      <color rgb="0035714F"/>
       <sz val="13"/>
     </font>
     <font>
@@ -97,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001D4E6B"/>
+        <fgColor rgb="0035714F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF2"/>
+        <fgColor rgb="00E9F2EC"/>
       </patternFill>
     </fill>
     <fill>
